--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1977,6 +1977,324 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128340285</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>745764</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7467063</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128340286</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>745879</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7466900</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128340044</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>745685</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7467038</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -1982,7 +1982,7 @@
         <v>128340285</v>
       </c>
       <c r="B14" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>128340286</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128340044</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2295,6 +2295,208 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130213076</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>745951</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7466878</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130213075</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>745926</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7466882</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -2300,7 +2300,7 @@
         <v>130213076</v>
       </c>
       <c r="B17" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130213075</v>
       </c>
       <c r="B18" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 41085-2025 artfynd.xlsx
+++ b/artfynd/A 41085-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79640914</v>
+        <v>130214824</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745679.1820735873</v>
+        <v>745788</v>
       </c>
       <c r="R2" t="n">
-        <v>7467088.103931231</v>
+        <v>7466900</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +769,69 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79640915</v>
+        <v>130214825</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745755.5536459079</v>
+        <v>745787</v>
       </c>
       <c r="R3" t="n">
-        <v>7467178.126072327</v>
+        <v>7466897</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79640791</v>
+        <v>130214827</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +898,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746401</v>
+        <v>745781</v>
       </c>
       <c r="R4" t="n">
-        <v>7466489</v>
+        <v>7466904</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,49 +981,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Anton Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79640896</v>
+        <v>79640786</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746059.0238831341</v>
+        <v>746233</v>
       </c>
       <c r="R5" t="n">
-        <v>7466788.27312705</v>
+        <v>7466436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,19 +1061,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 1,5 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,22 +1088,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79640897</v>
+        <v>127385485</v>
       </c>
       <c r="B6" t="n">
-        <v>93278</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,34 +1106,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2166</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lindb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746063.105869235</v>
+        <v>746244</v>
       </c>
       <c r="R6" t="n">
-        <v>7466786.310361876</v>
+        <v>7466422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,22 +1174,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Täckning 24 - 50%</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,30 +1196,26 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79640790</v>
+        <v>127385486</v>
       </c>
       <c r="B7" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1223,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746378.8544792195</v>
+        <v>746230</v>
       </c>
       <c r="R7" t="n">
-        <v>7466471.61131847</v>
+        <v>7466448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,22 +1291,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,30 +1313,26 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79640899</v>
+        <v>127385488</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1340,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746176.458743064</v>
+        <v>746155</v>
       </c>
       <c r="R8" t="n">
-        <v>7466661.111294451</v>
+        <v>7466539</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,22 +1408,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,69 +1430,75 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114653825</v>
+        <v>127385495</v>
       </c>
       <c r="B9" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745788</v>
+        <v>746102</v>
       </c>
       <c r="R9" t="n">
-        <v>7466927</v>
+        <v>7466578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,12 +1525,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Täckning 24 - 50%</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,52 +1547,48 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>inge Karlsson Alalahti</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114653681</v>
+        <v>127385496</v>
       </c>
       <c r="B10" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1593,16 +1596,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746178</v>
+        <v>746100</v>
       </c>
       <c r="R10" t="n">
-        <v>7466584</v>
+        <v>7466580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,12 +1642,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,69 +1664,75 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114653579</v>
+        <v>127385502</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746330</v>
+        <v>745986</v>
       </c>
       <c r="R11" t="n">
-        <v>7466402</v>
+        <v>7466675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,12 +1759,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,52 +1781,48 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114653722</v>
+        <v>127385503</v>
       </c>
       <c r="B12" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1805,16 +1830,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746282</v>
+        <v>745815</v>
       </c>
       <c r="R12" t="n">
-        <v>7466589</v>
+        <v>7466862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,12 +1876,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,30 +1898,26 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114653690</v>
+        <v>127385504</v>
       </c>
       <c r="B13" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,38 +1925,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745769</v>
+        <v>745816</v>
       </c>
       <c r="R13" t="n">
-        <v>7467004</v>
+        <v>7466869</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,12 +1993,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,47 +2015,48 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128340285</v>
+        <v>127385505</v>
       </c>
       <c r="B14" t="n">
-        <v>78881</v>
+        <v>101299</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2012,16 +2064,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Koskullskulle, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745764</v>
+        <v>745807</v>
       </c>
       <c r="R14" t="n">
-        <v>7467063</v>
+        <v>7466872</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,17 +2110,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,47 +2132,48 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128340286</v>
+        <v>127385507</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>101299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2118,16 +2181,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Koskullskulle, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745879</v>
+        <v>745797</v>
       </c>
       <c r="R15" t="n">
-        <v>7466900</v>
+        <v>7466881</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,17 +2227,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Täckning 10 - 25%</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,25 +2249,26 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128340044</v>
+        <v>127385508</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>101299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,21 +2276,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2224,16 +2298,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Koskullskulle, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745685</v>
+        <v>745795</v>
       </c>
       <c r="R16" t="n">
-        <v>7467038</v>
+        <v>7466884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,17 +2344,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2282,25 +2366,26 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130213076</v>
+        <v>127385509</v>
       </c>
       <c r="B17" t="n">
-        <v>97834</v>
+        <v>101299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,37 +2393,51 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745951</v>
+        <v>745789</v>
       </c>
       <c r="R17" t="n">
-        <v>7466878</v>
+        <v>7466891</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2362,12 +2461,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2379,29 +2483,26 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jennifer Sondell</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130213075</v>
+        <v>127385510</v>
       </c>
       <c r="B18" t="n">
-        <v>97834</v>
+        <v>101299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,37 +2510,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>1365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745926</v>
+        <v>745786</v>
       </c>
       <c r="R18" t="n">
-        <v>7466882</v>
+        <v>7466891</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2463,12 +2578,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,22 +2600,7484 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127385511</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>745788</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7466897</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127385512</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>745785</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7466898</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127385513</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>745779</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7466901</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127385514</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>745772</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7466909</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127385515</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>745769</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7466912</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127385516</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>745760</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7466924</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127385517</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>745758</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7466930</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127385518</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>745755</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7466933</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127385519</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>745751</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7466934</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127385520</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>745742</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7466946</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127385521</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>745735</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7466954</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127385522</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>745732</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7466960</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127385523</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>745728</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7466962</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Täckning 24 - 50%</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127385525</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>745672</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7467003</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127385526</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>745666</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7467005</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127385528</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>745666</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7467009</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127385529</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>745665</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7467009</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127385530</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>745661</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7467012</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127385531</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>745662</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7467018</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127385532</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>745658</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7467023</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127385533</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>745658</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7467025</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127385534</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>745653</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7467038</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127385535</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>745651</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7467042</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127385536</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>745650</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7467040</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127385538</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>745645</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7467040</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127385539</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>745639</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7467039</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127385540</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>745634</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7467044</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127385541</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>745634</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7467046</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127385542</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>745630</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7467047</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127385543</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>745626</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7467046</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127385544</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>745625</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7467045</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127385545</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Linaälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>745618</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7467058</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130214881</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>745783</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7466899</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
           <t>Irma Lindfors</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130214882</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>745787</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7466894</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130214883</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>745803</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7466878</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130214884</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>745803</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7466876</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130214885</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>745813</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7466865</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130214886</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101298</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>745836</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7466824</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128340287</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>746369</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7466379</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>79640897</v>
+      </c>
+      <c r="B58" t="n">
+        <v>96603</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skör kvastmossa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dicranum fragilifolium</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>746063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7466786</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>79640791</v>
+      </c>
+      <c r="B59" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>746401</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7466489</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128340044</v>
+      </c>
+      <c r="B60" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>745685</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7467038</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128340285</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>745764</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7467063</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128340286</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>745879</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7466900</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128340288</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Koskullskulle, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>746269</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7466430</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>79640896</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>746059</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7466788</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>79640777</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>746154</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7466541</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>114653825</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>745788</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7466927</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>inge Karlsson Alalahti</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129984328</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57369</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Leveäniemi, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>746522</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7466500</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>114653681</v>
+      </c>
+      <c r="B68" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>746178</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7466584</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>114653710</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>745891</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7467015</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>114653722</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>746282</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7466589</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>114776094</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>745774</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7466906</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>114653579</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>746330</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7466402</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>114653690</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>745769</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7467004</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130214765</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>745936</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7466717</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>79640785</v>
+      </c>
+      <c r="B75" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>746239</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7466437</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>79640790</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>746379</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7466472</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>79640910</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>745910</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7466760</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>79640914</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>745679</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7467088</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79640915</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>745756</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7467178</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130213075</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>745926</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7466882</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Jennifer Sondell</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY80" t="inlineStr">
         <is>
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130213076</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>745951</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7466878</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79640784</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>746259</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7466422</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>79640788</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>746235</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7466454</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>79640899</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>746176</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7466661</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>79640909</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>746048</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7466644</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130213040</v>
+      </c>
+      <c r="B86" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>745992</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7466899</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130214799</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>746020</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7466652</v>
+      </c>
+      <c r="S87" t="n">
+        <v>20</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
